--- a/data/climate_events.xlsx
+++ b/data/climate_events.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="12" min="1" max="1"/>
@@ -823,73 +823,102 @@
       </c>
       <c r="B32" s="23" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>--- 2026-09-21 addendum (Claude, atlas session — the original research chat was NOT reopened) ---</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Cross-checked this handoff package against the atlas's own copy of the register: the atlas copy was already ahead (293 events / 29 sources / 29 karst features vs 264/24/24 here), so nothing was missing.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>Then worked the open-items list as far as web search + the atlas's own station data would go:</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  #1 Knox Cave month: the 2025 Pomeroy Foundation historic marker independently says March 1975 — now 2 sources for March vs 1 for May vs 1 for 1976. Anchor updated to 1975-03 (month precision; day still not asserted). See Events row 141 and Sources.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  #3 Albany extremes: CONFIRMED against the current ALB_Extremes.pdf — 104°F Jul 4 1911 / -28°F Jan 19 1971, exactly as already recorded.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  #4 Frost/freeze phenology: built from Alcove Dam's own daily record (already in the atlas repo, no new upload needed) — see the new "Frost &amp; Freeze Phenology" sheet. 70-year and recent-30-year medians, full year-by-year table. Alcove Dam is ~590 ft, ~1,100 ft below Laurie's plateau — the best available regional anchor, not a plateau substitute.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  Bonus: Stone (2005 NCKMS) corrects McFail's own death to July 1, 1854 (not the widely repeated 1853 from Roscoe 1882) — logged in Sources. Did NOT find the historic-entrance collapse date (#2) — still open.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>STILL OPEN, genuinely unresolved by this pass (need the original chat's archive access or Laurie's own future work, not just web search):</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  #2 McFails historic-entrance collapse date. #5 Ludlum vol. II (1821-1870) — a physical/scanned book, not found online. #6 Fine-grained LiDAR sinkholes off Laurie's own parcel DEM — her own QGIS work (see the separate Westerlo_land_mapping package, which already ran this on her 25 acres and found NO karst there — see data/hilltowns_poi_lore_notes.md). #7 NYS Museum karst inventory / USGS SIR 2020-5030 Appendix 1 — not ingested. #8 Post-2012 tornado exact coordinates — would need the row-by-row NCEI lookup, not attempted this pass.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>The Folklore doc's lore items (Knox Cave legends, Old Skull bone-chamber, Clarksville wall carvings, Barton Hill "hollow hill") were appended to data/hilltowns_poi_lore_notes.md for the Lore Map — kept OUT of this register per the original project's own convention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>--- 2026-09-21 addendum #2 (Claude, atlas session) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Laurie sent a second handoff package (Westerlo_Climate_Register_HANDOFF_v2) from the original research chat, which had branched forward independently after the first handoff — the two branches genuinely diverged (mine has the Knox Cave date fix + 4 new sources + the Frost sheet; v2 has 5 newly researched karst features with real published/USGS coordinates and a full coordinate pass on the whole Karst sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Merged v2 into this file: 21 existing Subsidence &amp; Karst rows got real coordinates (replacing hamlet-centroid guesses) and 4 new coordinate/precision/source columns; 5 new features added (Natural Stone Bridge &amp; Caves, Bartholomew's Cobble/Eldon's Cave, Rosendale/Widow Jane Mine, Tory Cave, Wolf Hollow) plus the scope-note and carbonate-belt-polygon rows. Matching Geology-layer pins updated/added in data/points_of_interest.xlsx; Tory Cave's 1777 Loyalist-spy lore also added to the Folklore layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>v2 did NOT carry my Knox Cave date fix or the 4 new sources forward — those stay atlas-only unless the original chat is refreshed from here.</t>
         </is>
       </c>
     </row>
@@ -65090,7 +65119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="12" min="1" max="1"/>
@@ -65138,6 +65167,26 @@
           <t>Status / notes</t>
         </is>
       </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>Lat</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>Lon</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>Coord precision</t>
+        </is>
+      </c>
+      <c r="K1" s="12" t="inlineStr">
+        <is>
+          <t>Coord source / note</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="57" customHeight="1" s="13">
       <c r="A2" s="19" t="inlineStr">
@@ -65175,6 +65224,22 @@
           <t>ACTIVE karst sink. 1975 fatal ice collapse (see Events). NCC preserve, permit required. 72 new timber steps Aug 2025.</t>
         </is>
       </c>
+      <c r="H2" s="12" t="n">
+        <v>42.6697</v>
+      </c>
+      <c r="I2" s="12" t="n">
+        <v>-74.1182</v>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>access/marker locus</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>2025 Pomeroy/Knox Hist. Soc. marker on Berne-Altamont Rd (Rte 156); cave off Knox Cave Rd, 'located nearby' - NCC permit, exact entrance not published. HMdb/WGP Foundation.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="90.75" customHeight="1" s="13">
       <c r="A3" s="19" t="inlineStr">
@@ -65212,6 +65277,22 @@
           <t>ACTIVE. Prone to sudden flooding after intense rain. A cornfield sink is forming between entrance &amp; road; Irene opened an 18-in x 6-ft hole (2011, see Events). NCC preserve.</t>
         </is>
       </c>
+      <c r="H3" s="12" t="n">
+        <v>42.565</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>-73.98</v>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>vicinity (approx)</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>Clarksville / New Scotland, ~1 mi SW of Clarksville hamlet; NCC permit-only, floods; exact entrance not published. Approximate - verify.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="102" customHeight="1" s="13">
       <c r="A4" s="19" t="inlineStr">
@@ -65249,6 +65330,22 @@
           <t>ACTIVE. Most-visited non-commercial cave in the Northeast; periodic rescues. NCC preserve.</t>
         </is>
       </c>
+      <c r="H4" s="12" t="n">
+        <v>42.5758</v>
+      </c>
+      <c r="I4" s="12" t="n">
+        <v>-73.9639</v>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>hamlet locus</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>Clarksville hamlet just off Rte 443; NCC preserve open to public; hamlet-centroid locus (Wikipedia/NCC).</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="23.25" customHeight="1" s="13">
       <c r="A5" s="19" t="inlineStr">
@@ -65286,6 +65383,22 @@
           <t>ACTIVE sink. NCC preserve near Knox &amp; Skull caves.</t>
         </is>
       </c>
+      <c r="H5" s="12" t="n">
+        <v>42.665</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>-74.125</v>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>cluster locus (exact not public)</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>Knox cluster, near Knox &amp; Skull caves; NCC; exact entrance not published. Shares Knox-crest locus.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="13">
       <c r="A6" s="19" t="inlineStr">
@@ -65319,6 +65432,22 @@
           <t>Near Knox Cave; on the same karst crest.</t>
         </is>
       </c>
+      <c r="H6" s="12" t="n">
+        <v>42.665</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>-74.125</v>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>cluster locus (exact not public)</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>Knox cluster, on Middle Rd near Knox Cave; exact entrance not published. Shares Knox-crest locus.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="13">
       <c r="A7" s="19" t="inlineStr">
@@ -65352,6 +65481,22 @@
           <t>ACTIVE karst zone bounded W by Hamilton shale hills, E by the Onondaga escarpment.</t>
         </is>
       </c>
+      <c r="H7" s="12" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>-73.95</v>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>bench locus (approx)</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>New Scotland Onondaga karst bench, part of the Onesquethaw-Clarksville zone; sinks/resurgences, not a single point. Approximate.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="57" customHeight="1" s="13">
       <c r="A8" s="19" t="inlineStr">
@@ -65389,6 +65534,22 @@
           <t>ACTIVE. Historic entrance became unstable and COLLAPSED (see Events, date approx). NSS-owned, NCC-managed. Wetsuit required; trips up to 12 hrs.</t>
         </is>
       </c>
+      <c r="H8" s="12" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>-74.43000000000001</v>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>approx (triangulated)</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>Carlisle (Cobleskill quad); NSS McFails Cave Nature Preserve - historic 'McFails Hole' entrance (+ Halls Hole, Coeymans Dome Sink parcels); landlocked, entrance not published; DEC unique-geologic-feature. Placed ~12 mi W of Gage Preserve. Approx - verify. LiDAR inventory: no match (nearest is an anthropogenic detention basin 2.8 mi W).</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="23.25" customHeight="1" s="13">
       <c r="A9" s="19" t="inlineStr">
@@ -65422,6 +65583,22 @@
           <t>Karst resurgence / spring — the discharge end of the McFails system.</t>
         </is>
       </c>
+      <c r="H9" s="12" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>-74.41500000000001</v>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>approx</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>McFails-system karst resurgence discharging toward Cobleskill Creek, ~2 mi from McFails Hole; approx - verify.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="34.5" customHeight="1" s="13">
       <c r="A10" s="19" t="inlineStr">
@@ -65459,6 +65636,22 @@
           <t>ACTIVE karst complex. The plateau above Cobleskill is pockmarked with sinkholes 70+ ft deep swallowing streams.</t>
         </is>
       </c>
+      <c r="H10" s="12" t="n">
+        <v>42.6965</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>-74.3986</v>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>published point (anchor)</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>Anchored at Howe Caverns 42.6965,-74.3986 (255 Discovery Dr, commercial; Wikipedia). Secret Caverns 42.7091,-74.3913 (671 Caverns Rd). Complex spans several km of the Cobleskill plateau.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="34.5" customHeight="1" s="13">
       <c r="A11" s="19" t="inlineStr">
@@ -65496,6 +65689,22 @@
           <t>NSS-owned (donated by Jim Gage). Cabin on site for visiting cavers. Barton Hill is riddled with caves.</t>
         </is>
       </c>
+      <c r="H11" s="12" t="n">
+        <v>42.67869</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>-74.24263000000001</v>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>USGS NWIS gage locus</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>USGS NWIS gage 01351150 'Schoharie Cavern at Shutter Corners' (1:24000, NAD83) - the cave's own stream-monitoring point; best-anchored Barton Hill cave. Entrance at the plateau edge above Fox/Schoharie creeks.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="23.25" customHeight="1" s="13">
       <c r="A12" s="19" t="inlineStr">
@@ -65529,6 +65738,22 @@
           <t>NSS-owned: the James Gage Karst Preserve (Barton Hill), donated by the Gage family. Cave named for its 19th-c. landowner.</t>
         </is>
       </c>
+      <c r="H12" s="12" t="n">
+        <v>42.678</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>-74.24299999999999</v>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>cluster locus (exact not public)</t>
+        </is>
+      </c>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>James Gage Karst Preserve, Barton Hill ridge; re-anchored near the Schoharie Cavern USGS gage (Shutters Corners), ~9 mi W of Knox / 12 mi E of McFails per NSS; exact entrance not published. Cluster locus (~2-3 mi ridge spread).</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="23.25" customHeight="1" s="13">
       <c r="A13" s="19" t="inlineStr">
@@ -65562,6 +65787,22 @@
           <t>Recently donated to the NCC by a local landowner.</t>
         </is>
       </c>
+      <c r="H13" s="12" t="n">
+        <v>42.678</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>-74.24299999999999</v>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>cluster locus (exact not public)</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>Barton Hill ridge (NCC), near the Schoharie Cavern USGS gage (Shutters Corners); exact entrance not published. Cluster locus.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="45.75" customHeight="1" s="13">
       <c r="A14" s="19" t="inlineStr">
@@ -65595,6 +65836,22 @@
           <t>ACTIVE insurgence sink. Illustrates the limestone/shale contact that localizes plateau karst; marks the toe of the Catskill Delta.</t>
         </is>
       </c>
+      <c r="H14" s="12" t="n">
+        <v>42.63428</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>-74.02888</v>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>LiDAR depression (probable match)</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>Matched to USGS LiDAR closed depression LiDAR-36-001-16 (Onondaga Ls, natural, drainage-terminating 'sinkhole' signature), 0.5 mi WSW of the Beaver Dam Rd landmark estimate. PROBABLE identity - a natural Onondaga insurgence at the right contact, but not field-confirmed as the exact TV Tower entrance. Verify.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="45.75" customHeight="1" s="13">
       <c r="A15" s="19" t="inlineStr">
@@ -65632,6 +65889,22 @@
           <t>FILLED / ERASED feature. A mid-1800s farmer dumped boulders then dirt into it after reportedly finding human &amp; large-animal bones (steer or Ice-Age ground sloth, per legend) on the chamber floor. Deliberately obliterated by hand - a human-filled karst sink.</t>
         </is>
       </c>
+      <c r="H15" s="12" t="n">
+        <v>42.665</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>-74.125</v>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>cluster locus (exact not public)</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>Knox, a few hundred yards from Knox &amp; New Skull; FILLED/erased feature. Knox-crest locus.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="34.5" customHeight="1" s="13">
       <c r="A16" s="19" t="inlineStr">
@@ -65669,6 +65942,22 @@
           <t>ACTIVE, off-limits to sport cavers for years. Named for the nearby Old Skull sinkhole.</t>
         </is>
       </c>
+      <c r="H16" s="12" t="n">
+        <v>42.665</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>-74.125</v>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>cluster locus (exact not public)</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>Knox, &lt;1000 ft from Knox Cave; off-limits. Knox-crest locus; exact entrance not published.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="57" customHeight="1" s="13">
       <c r="A17" s="19" t="inlineStr">
@@ -65706,6 +65995,22 @@
           <t>ACTIVE stream-swallowing sink on private land (Loden family since 1918). Chronic illegal dumping (carcasses, tires, trash) enters the aquifer directly — a karst water-quality hazard. Near Skull Cave, also on Middle Rd. DEC notified 2014.</t>
         </is>
       </c>
+      <c r="H17" s="12" t="n">
+        <v>42.66</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>-74.20999999999999</v>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>approx</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>Wright (Schoharie Co.), Middle Rd; large enough to show on topo maps; private land. Approximate - verify from topo. LiDAR inventory: no natural carbonate match within 2 mi (nearest is 2.4 mi E, Albany Co.).</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="57" customHeight="1" s="13">
       <c r="A18" s="19" t="inlineStr">
@@ -65780,6 +66085,22 @@
           <t>Known cave (Nardacci, Altamont Enterprise 21 Apr 2016). Coordinates/dimensions NEEDED — Mylroie 1977 (NY Cave Survey Bull. 2) is the systematic source. Confidence C.</t>
         </is>
       </c>
+      <c r="H19" s="12" t="n">
+        <v>42.678</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>-74.24299999999999</v>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>cluster locus (exact not public)</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>Barton Hill ridge (Gallupville/Shutters Corners), dip-parallel set; exact entrance not published. Cluster locus.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="13">
       <c r="A20" s="19" t="inlineStr">
@@ -65817,6 +66138,22 @@
           <t>Known cave (Nardacci 2016). Coordinates/dimensions NEEDED. Confidence C.</t>
         </is>
       </c>
+      <c r="H20" s="12" t="n">
+        <v>42.678</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>-74.24299999999999</v>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>cluster locus (exact not public)</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>Barton Hill ridge (Gallupville/Shutters Corners); exact entrance not published. Cluster locus.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="13">
       <c r="A21" s="19" t="inlineStr">
@@ -65854,6 +66191,22 @@
           <t>Named occluded sinkhole (Nardacci 2016), Barton Hill. Coordinates NEEDED. Confidence C.</t>
         </is>
       </c>
+      <c r="H21" s="12" t="n">
+        <v>42.678</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>-74.24299999999999</v>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>cluster locus (exact not public)</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>Barton Hill ridge (Gallupville/Shutters Corners); occluded sinkhole; exact location not published. Cluster locus.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="13">
       <c r="A22" s="19" t="inlineStr">
@@ -65891,6 +66244,22 @@
           <t>ACTIVE. A lowland Onondaga karst pocket SE of the escarpment cluster — the register's first Ravena/Coeymans-area feature. Nardacci 'Back Roads Geology'.</t>
         </is>
       </c>
+      <c r="H22" s="12" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>-73.88</v>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>park locus (approx)</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>Joralemon Park, Rte 102 (Starr Rd), Coeymans; lowland Onondaga karst; approximate park locus - verify.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="13">
       <c r="A23" s="19" t="inlineStr">
@@ -65926,6 +66295,22 @@
       <c r="G23" s="19" t="inlineStr">
         <is>
           <t>Named cave (Nardacci 'Back Roads Geology'). Coordinates/dimensions NEEDED. Lowland Onondaga karst near Ravena.</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>-73.88</v>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>park locus (approx)</t>
+        </is>
+      </c>
+      <c r="K23" s="12" t="inlineStr">
+        <is>
+          <t>Joralemon Park, E side of Rte 102, Coeymans; approximate park locus - verify. Distinct feature from Hannacroix Maze within the same park.</t>
         </is>
       </c>
     </row>
@@ -65964,6 +66349,349 @@
           <t>SYSTEMATIC DATA SOURCES (the way to catch collapses no newspaper covered): (1) USGS Kappel et al. 2020, Statewide Assessment of Karst Aquifers in NY, SIR 2020-5030 - GIS karst datasets, closed depressions, karst-prone bedrock, incl. Knox Cave. (2) USGS SIR 2021-5094, Albany-Buffalo karst aquifer methods. (3) SUNY Brockport (Paul Richards) LiDAR study of Albany Co. karst, 2014-15: classified 2,174 Definitely Karst / 412 Not Karst / 2,775 Possible Karst features, 150 field surveys, 17 GPR profiles. (4) Cornell karst / manure-management database (hydrology.bee.cornell.edu/Karst_Webpage). These are the register-grade inventory sources; the Nardacci columns are narrative color.</t>
         </is>
       </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>Natural Stone Bridge &amp; Caves</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Pottersville (Horicon, Warren Co.) — LOWER ADK</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>Grenville MARBLE (~1.1 Ga metamorphic — NOT Helderberg limestone)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>11-cave marble-karst system, potholes &amp; grottos along an E-W fault; 'largest marble cave entrance in the East'</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>show trail ~0.75 mi; 43.7475,-73.8523, 929 ft</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>Trout Brook sinks, runs underground, resurfaces ~200 m away at 'The Clamshell' pothole</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>Commercial show cave (Path Through History). Rapidly dissolved by acidic glacial meltwater. NEW ROCK TYPE for this sheet — marble, not Devonian limestone. Verified (Wikipedia/park).</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>43.7475</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>-73.8523</v>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>published point</t>
+        </is>
+      </c>
+      <c r="K30" s="12" t="inlineStr">
+        <is>
+          <t>Commercial show cave, Pottersville (Horicon, Warren Co.); published (park/Wikipedia). Grenville marble.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>Bartholomew's Cobble (Eldon's Cave)</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Ashley Falls, Sheffield (Berkshire Co., MA) — TACONIC / BERKSHIRE</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>Stockbridge (Cambro-Ordovician) MARBLE</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>Two marble-karst knolls ('the Cobbles'); Eldon's Cave is a marble cave with a 'Disappearing Brook'</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>329-acre preserve; 42.0572,-73.3508</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>Disappearing/resurging brook in the marble; Housatonic/Konkapot floodplain</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>Trustees of Reservations; National Natural Landmark (1971). Berkshire marble karst, ACROSS the Hudson in the Housatonic valley. Verified.</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>42.0572</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>-73.35080000000001</v>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>published point</t>
+        </is>
+      </c>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>Trustees of Reservations preserve; National Natural Landmark; published point. Stockbridge marble.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>Rosendale karst &amp; cement district (Widow Jane Mine)</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Rosendale (Ulster Co.) — MID-HUDSON</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>Rondout dolostone / Onondaga limestone</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>Natural karst + the famous Rosendale natural-CEMENT mines (Widow Jane Mine); Binnewater lakes are karst-fed</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>Karst springs; the flooded cement mines host bats</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>Grade C — the cement MINES are anthropogenic but sit in genuine Rondout/Onondaga karst. POI + karst. Verify extent in a fresh session.</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>41.8416</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>-74.0988</v>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
+        <is>
+          <t>published point (anchor)</t>
+        </is>
+      </c>
+      <c r="K32" s="12" t="inlineStr">
+        <is>
+          <t>Widow Jane Mine, Century House Historical District, 668 NY-213, Rosendale; published (showcaves/Backroads). Anchors the Rondout/Onondaga karst + cement district.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>Tory Cave</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Voorheesville / New Scotland (Thacher Park, Albany Co.)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>Coeymans &amp; Manlius Ls (Helderberg Grp)</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>Escarpment-top limestone cave near the Indian Ladder Trail; entrance a hidden cleft among the cliffs; a natural chimney/flue rises from the rear chamber to the surface above</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>Small single chamber with a rear chimney; most formations stripped by 19th-c. collectors</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>Seepage-fed; the chimney vents air so spring meltwater builds unusually large ICE stalagmites (a partial rockfall blocks the drafts that would otherwise prevent them)</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>Historic 'Tory Cave': in 1777 Loyalist spy Jacob Salsbury sheltered here after raiding valley farms; fire-smoke rose through the chimney and betrayed him (captured/hanged, per lore). In John Boyd Thacher State Park near Indian Ladder; same Coeymans/Manlius cave-former as Howe &amp; Secret. Verified (Wikipedia/HMdb/DAR).</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>42.65547</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>-74.01687</v>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>access/marker locus</t>
+        </is>
+      </c>
+      <c r="K33" s="12" t="inlineStr">
+        <is>
+          <t>1994 Tawasentha DAR 'Tory Cave 1777' marker at the Indian Ladder trailhead, Thacher Park (Rte 157); the cave is ~0.3 mi from the marker near the escarpment top. HMdb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>Wolf Hollow (Hoffmans Fault gorge)</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>Glenville (Schenectady Co.), Hoffmans</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>FAULT gorge - NOT karst: Hoffmans normal fault juxtaposing Schenectady Fm sandstone/shale (E) against Beekmantown dolostone + Trenton Ls (W)</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>~1-mi confined gorge of Chaughtanoonda Creek cut ALONG the fault by differential erosion + glacial meltwater; cliffs to ~200 ft; not a cave or sink</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>~1 mi long; ~1000 ft of fault displacement; cliffs ~100-200 ft</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>Chaughtanoonda Creek runs the gorge floor from the Glenville Hills to the Mohawk at Hoffmans - surface drainage, not a karst conduit</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>NOT KARST - a FAULT-LINE GORGE (differential erosion along the Hoffmans Fault). Filed as a flagged non-karst contrast (cf. the Catskills &amp; Mohawk scope notes) so it isn't mis-added as dissolution karst. Mohawk Hudson Land Conservancy ~400 ac; walkers' road off Rte 5. Also the 1669 Mohawk-Algonquian battle site (Kinaquariones). Verified (Union College/Garver; HMdb).</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>42.91</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>-74.072</v>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>gorge-midpoint locus</t>
+        </is>
+      </c>
+      <c r="K34" s="12" t="inlineStr">
+        <is>
+          <t>Midpoint of the ~1-mi Wolf Hollow Rd gorge, bracketed by DAR markers at 42.9040,-74.0742 (S) and 42.9175,-74.0697 (N); linear feature, so the point is a placeholder. Access off Rte 5 (Amsterdam Rd). HMdb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>GEOLOGICAL SCOPE NOTE — CATSKILLS PROPER = NON-KARST: the high Catskills (Greene/Delaware/Ulster) are Devonian sandstone/shale (Catskill-delta clastics) with NO solution karst. The 'greater-Catskill' karst IS the Helderberg/Schoharie/Onondaga CARBONATE MARGIN inventoried above. The Shawangunk 'Ice Caves' (Sam's Point, Ellenville) are conglomerate CREVICE/TALUS caves, not dissolution karst.</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="23" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>GEOLOGICAL SCOPE NOTE — MOHAWK VALLEY karst is LIMITED: the Helderberg/Onondaga carbonate belt thins westward; only minor karst (e.g., Little Falls dolostone). Wolf Hollow (Glenville) is a FAULT gorge, not karst. The dense cave country is the Schoharie/Helderberg belt to the south.</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="n"/>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="23" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>EXPANSION STATUS (added this session): marble karst — Natural Stone Bridge (lower ADK) + Bartholomew's Cobble/Eldon's Cave (Berkshire) — plus Rosendale (mid-Hudson). STILL TO ADD in a fresh session (context-limited): more Schoharie show/wild caves (Gage Caverns, Ball's Cave detail, Gebhard/Central Bridge), Kingston-area Onondaga karst, additional Berkshire/Taconic marble caves (Salisbury CT, Beartown/Stockbridge), and coordinates/DEM placement for map layers.</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="n"/>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="23" t="n"/>
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="23" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>MAP LAYER - REGIONAL CARBONATE-BELT FILL: the 'Helderberg-Cobleskill karst (regional)' row is an areal province (~40 mi of carbonate outcrop), NOT a point. Render it as a translucent POLYGON fill UNDER the cave markers. Use the authoritative carbonate polygon (kn11) for a real fill; the placeholder below (kn10) only brackets the known cave clusters.</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="n"/>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="23" t="n"/>
+      <c r="F38" s="23" t="n"/>
+      <c r="G38" s="23" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>Placeholder envelope (APPROXIMATE coarse hull around the cave clusters, NOT the true carbonate contact). WKT (lon-lat): POLYGON((-73.92 42.53, -74.22 42.58, -74.40 42.63, -74.50 42.66, -74.47 42.74, -74.25 42.76, -74.00 42.72, -73.90 42.64, -73.92 42.53)). Leaflet [lat,lon]: [[42.53,-73.92],[42.58,-74.22],[42.63,-74.40],[42.66,-74.50],[42.74,-74.47],[42.76,-74.25],[42.72,-74.00],[42.64,-73.90],[42.53,-73.92]]. NB WKT is lon-lat, Leaflet is lat-lon - do not swap the axes.</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="n"/>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="23" t="n"/>
+      <c r="F39" s="23" t="n"/>
+      <c r="G39" s="23" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Authoritative fill source (replace the placeholder): USGS Kappel 2020, Statewide Assessment of Karst Aquifers in NY, SIR 2020-5030 - the 'karst-prone bedrock' (carbonate outcrop) GIS layer, ScienceBase data release. Alt: NYS Museum bedrock carbonate units (Manlius, Coeymans, Kalkberg, New Scotland, Becraft, Onondaga) via the NYS GIS Clearinghouse. Clip to the ~75-mi footprint.</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="n"/>
+      <c r="C40" s="23" t="n"/>
+      <c r="D40" s="23" t="n"/>
+      <c r="E40" s="23" t="n"/>
+      <c r="F40" s="23" t="n"/>
+      <c r="G40" s="23" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G23"/>

--- a/data/climate_events.xlsx
+++ b/data/climate_events.xlsx
@@ -823,7 +823,6 @@
       </c>
       <c r="B32" s="23" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
@@ -895,28 +894,28 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>--- 2026-09-21 addendum #2 (Claude, atlas session) ---</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Laurie sent a second handoff package (Westerlo_Climate_Register_HANDOFF_v2) from the original research chat, which had branched forward independently after the first handoff — the two branches genuinely diverged (mine has the Knox Cave date fix + 4 new sources + the Frost sheet; v2 has 5 newly researched karst features with real published/USGS coordinates and a full coordinate pass on the whole Karst sheet).</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Merged v2 into this file: 21 existing Subsidence &amp; Karst rows got real coordinates (replacing hamlet-centroid guesses) and 4 new coordinate/precision/source columns; 5 new features added (Natural Stone Bridge &amp; Caves, Bartholomew's Cobble/Eldon's Cave, Rosendale/Widow Jane Mine, Tory Cave, Wolf Hollow) plus the scope-note and carbonate-belt-polygon rows. Matching Geology-layer pins updated/added in data/points_of_interest.xlsx; Tory Cave's 1777 Loyalist-spy lore also added to the Folklore layer.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>v2 did NOT carry my Knox Cave date fix or the 4 new sources forward — those stay atlas-only unless the original chat is refreshed from here.</t>
         </is>
@@ -35557,7 +35556,7 @@
       </c>
       <c r="G266" s="19" t="inlineStr">
         <is>
-          <t>Irene drowning – Sharon Stein, Onesquethaw Creek</t>
+          <t>Irene flood drowning, Onesquethaw Creek</t>
         </is>
       </c>
       <c r="H266" s="19" t="inlineStr">
@@ -35567,7 +35566,7 @@
       </c>
       <c r="I266" s="19" t="inlineStr">
         <is>
-          <t>1 drowning: Sharon Stein, 68, swept from her creek-side home by the flooding Onesquethaw while packing to evacuate; body recovered the same day</t>
+          <t>1 drowning: a 68-year-old resident swept from her creek-side home by the flooding Onesquethaw while packing to evacuate; body recovered the same day</t>
         </is>
       </c>
       <c r="J266" s="19" t="inlineStr">
@@ -35598,7 +35597,7 @@
       </c>
       <c r="P266" s="19" t="inlineStr">
         <is>
-          <t>Coordinates approximate (~42.60,-74.00); verify. Companion to the Onesquethaw Irene sinkhole row and the 1991 Onesquethaw flood.</t>
+          <t>Coordinates approximate (~42.60,-74.00); verify. Companion to the Onesquethaw Irene sinkhole row and the 1991 Onesquethaw flood. UPDATE 2026-09-21: named victim removed per Laurie — kept as an anonymized hazard record (age, mechanism, location); do not re-add a name.</t>
         </is>
       </c>
       <c r="Q266" s="19" t="inlineStr">
@@ -35658,7 +35657,7 @@
       </c>
       <c r="G267" s="19" t="inlineStr">
         <is>
-          <t>Irene drowning – Stephen Terleckey, Route 5S</t>
+          <t>Irene flood drowning, Route 5S</t>
         </is>
       </c>
       <c r="H267" s="19" t="inlineStr">
@@ -35668,7 +35667,7 @@
       </c>
       <c r="I267" s="19" t="inlineStr">
         <is>
-          <t>1 drowning: Stephen Terleckey, 72, of Amsterdam, drove a pickup past barriers onto a washed-out section of Route 5S the day after Irene and drowned</t>
+          <t>1 drowning: a 72-year-old man drove a pickup past barriers onto a washed-out section of Route 5S the day after Irene and drowned</t>
         </is>
       </c>
       <c r="J267" s="19" t="inlineStr">
@@ -35699,7 +35698,7 @@
       </c>
       <c r="P267" s="19" t="inlineStr">
         <is>
-          <t>Coordinates approximate along the 5S corridor; verify.</t>
+          <t>Coordinates approximate along the 5S corridor; verify. UPDATE 2026-09-21: named victim removed per Laurie — kept as an anonymized hazard record (age, mechanism, location); do not re-add a name.</t>
         </is>
       </c>
       <c r="Q267" s="19" t="inlineStr">
@@ -35759,7 +35758,7 @@
       </c>
       <c r="G268" s="19" t="inlineStr">
         <is>
-          <t>Irene indirect death – Elizabeth Slagle, McKownville</t>
+          <t>Irene indirect death, McKownville</t>
         </is>
       </c>
       <c r="H268" s="19" t="inlineStr">
@@ -35769,7 +35768,7 @@
       </c>
       <c r="I268" s="19" t="inlineStr">
         <is>
-          <t>1 indirect death: Elizabeth Slagle, 88, fell down her basement stairs while checking flooding; found Aug 29. Guilderland police classified it 'secondary'</t>
+          <t>1 indirect death: an 88-year-old resident fell down her basement stairs while checking flooding; found Aug 29. Guilderland police classified it 'secondary'</t>
         </is>
       </c>
       <c r="J268" s="19" t="inlineStr">
@@ -35800,7 +35799,7 @@
       </c>
       <c r="P268" s="19" t="inlineStr">
         <is>
-          <t>'Secondary' per Guilderland PD (interpretive). Coordinates approximate (~42.688,-73.852); verify.</t>
+          <t>'Secondary' per Guilderland PD (interpretive). Coordinates approximate (~42.688,-73.852); verify. UPDATE 2026-09-21: named victim removed per Laurie — kept as an anonymized hazard record (age, mechanism, location); do not re-add a name.</t>
         </is>
       </c>
       <c r="Q268" s="19" t="inlineStr">
